--- a/outputs/20260809/idf_availability_summary_by_idf.xlsx
+++ b/outputs/20260809/idf_availability_summary_by_idf.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -385,6 +385,11 @@
           <t>availability_pct</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>availability_cat</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -407,6 +412,11 @@
       <c r="F2">
         <v>95.90000000000001</v>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>90-96%</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -429,6 +439,11 @@
       <c r="F3">
         <v>96.90000000000001</v>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>&gt;96%</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -451,6 +466,11 @@
       <c r="F4">
         <v>96.90000000000001</v>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>&gt;96%</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -472,6 +492,11 @@
       </c>
       <c r="F5">
         <v>97</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>&gt;96%</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/outputs/20260809/idf_availability_summary_by_idf.xlsx
+++ b/outputs/20260809/idf_availability_summary_by_idf.xlsx
@@ -398,46 +398,46 @@
         </is>
       </c>
       <c r="B2">
-        <v>4793.9</v>
+        <v>4874.5</v>
       </c>
       <c r="C2">
-        <v>117888.7666666667</v>
+        <v>182085.4666666667</v>
       </c>
       <c r="D2">
-        <v>150</v>
+        <v>259</v>
       </c>
       <c r="E2">
-        <v>4.1</v>
+        <v>2.7</v>
       </c>
       <c r="F2">
-        <v>95.90000000000001</v>
+        <v>97.3</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>90-96%</t>
+          <t>&gt;96%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BSH52-11</t>
+          <t>BSH70-02</t>
         </is>
       </c>
       <c r="B3">
-        <v>3601.883333333333</v>
+        <v>3761.233333333333</v>
       </c>
       <c r="C3">
-        <v>117888.7666666667</v>
+        <v>182085.4666666667</v>
       </c>
       <c r="D3">
-        <v>150</v>
+        <v>259</v>
       </c>
       <c r="E3">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="F3">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -448,23 +448,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BSH70-02</t>
+          <t>BSH52-11</t>
         </is>
       </c>
       <c r="B4">
-        <v>3620.633333333333</v>
+        <v>3682.483333333334</v>
       </c>
       <c r="C4">
-        <v>117888.7666666667</v>
+        <v>182085.4666666667</v>
       </c>
       <c r="D4">
-        <v>150</v>
+        <v>259</v>
       </c>
       <c r="E4">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>96.90000000000001</v>
+        <v>98</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -479,19 +479,19 @@
         </is>
       </c>
       <c r="B5">
-        <v>3543.45</v>
+        <v>3684.05</v>
       </c>
       <c r="C5">
-        <v>117888.7666666667</v>
+        <v>182085.4666666667</v>
       </c>
       <c r="D5">
-        <v>150</v>
+        <v>259</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
